--- a/templates/excel/Pre_Contract_Clarifications_TEMPLATE.xlsx
+++ b/templates/excel/Pre_Contract_Clarifications_TEMPLATE.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Clarifications" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Instructions" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -702,7 +702,7 @@
         <v>17</v>
       </c>
       <c r="B2" s="5" t="n">
-        <f aca="false">Setup!B12</f>
+        <f aca="false">Setup!B13</f>
         <v>0</v>
       </c>
     </row>
